--- a/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Revenue/Revenue_Descriptive_Statistics.xlsx
+++ b/AIGGPA_Fieldwork_Review/Department_Wise_Analysis/Revenue/Revenue_Descriptive_Statistics.xlsx
@@ -548,34 +548,34 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>3.15</v>
-      </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="3">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2</v>
@@ -603,16 +603,16 @@
         <v>5</v>
       </c>
       <c r="H3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>3.25</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -640,16 +640,16 @@
         <v>5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>1</v>
@@ -677,16 +677,16 @@
         <v>5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.85</v>
+        <v>4.5</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
@@ -714,16 +714,16 @@
         <v>5</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -733,16 +733,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>1</v>
@@ -751,16 +751,16 @@
         <v>5</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
@@ -770,16 +770,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
@@ -788,16 +788,16 @@
         <v>5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>1</v>
@@ -825,16 +825,16 @@
         <v>5</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1</v>
@@ -862,16 +862,16 @@
         <v>5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>5</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -918,16 +918,16 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
@@ -936,16 +936,16 @@
         <v>5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>2.65</v>
+        <v>4.5</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>1</v>
@@ -973,16 +973,16 @@
         <v>5</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14">
@@ -992,16 +992,16 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>1</v>
@@ -1010,16 +1010,16 @@
         <v>4</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15">
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>1</v>
@@ -1047,16 +1047,16 @@
         <v>4</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16">
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
@@ -1084,16 +1084,16 @@
         <v>5</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="17">
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>1</v>
@@ -1121,16 +1121,16 @@
         <v>4</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18">
@@ -1140,16 +1140,16 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
@@ -1158,16 +1158,16 @@
         <v>4</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1177,16 +1177,16 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>1</v>
@@ -1195,16 +1195,16 @@
         <v>5</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
@@ -1232,16 +1232,16 @@
         <v>5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21">
@@ -1251,16 +1251,16 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>3</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>1</v>
@@ -1269,16 +1269,16 @@
         <v>4</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="22">
@@ -1288,16 +1288,16 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
@@ -1306,16 +1306,16 @@
         <v>5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1325,16 +1325,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>1</v>
@@ -1343,16 +1343,16 @@
         <v>4</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1367,7 +1367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1406,49 +1406,49 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>35</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Agree</t>
+          <t>Strongly agree</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Disagree somewhat</t>
+          <t>Agree</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Strongly agree</t>
+          <t>Disagree somewhat</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>20</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="8">
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>55</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="11">
@@ -1498,7 +1498,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="12">
@@ -1511,7 +1511,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>20</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="14">
@@ -1545,36 +1545,36 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>45</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>shared phone</t>
+          <t>desktop, laptop, phone</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>desktop, laptop, phone</t>
+          <t>shared phone</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="19">
@@ -1587,7 +1587,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="20">
@@ -1600,7 +1600,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="21">
@@ -1613,7 +1613,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="22">
@@ -1626,7 +1626,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="24">
@@ -1656,292 +1656,292 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>30</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Rarely</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>Very often</t>
+          <t>Often</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Very often</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
+          <t>Sometimes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t>Never</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="6" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="C31" s="6" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Q24_Helpdesk</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B36" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C35" s="6" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="C36" s="6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Q27_PctDigital</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>41-60%</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>21-40%</t>
+          <t>81-100%</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>0-20%</t>
+          <t>41-60%</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>20</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>61-80%</t>
+          <t>21-40%</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>81-100%</t>
+          <t>0-20%</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>61-80%</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Q36_NonGovtApps</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>70</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>77.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B49" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C48" s="6" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="C49" s="6" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Q44_Training</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="C52" s="6" t="n">
-        <v>55</v>
       </c>
     </row>
     <row r="53">
@@ -1951,123 +1951,123 @@
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+        <v>59.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Q50_BeyondSkill</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C57" s="6" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B59" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="C58" s="6" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="C59" s="6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Q61_PaperPct</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>41-60%</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C62" s="6" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>81-100%</t>
+          <t>41-60%</t>
         </is>
       </c>
       <c r="B63" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>30</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>61-80%</t>
+          <t>81-100%</t>
         </is>
       </c>
       <c r="B64" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="65">
@@ -2077,23 +2077,36 @@
         </is>
       </c>
       <c r="B65" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
+          <t>61-80%</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>14.8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
           <t>0-20%</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="6" t="n">
-        <v>5</v>
+      <c r="B67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>3.7</v>
       </c>
     </row>
   </sheetData>
